--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-15 13:01:00</t>
+          <t>Timestamp: 2026-07-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>10226</v>
+        <v>10256</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>14528</v>
+        <v>14558</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>19390</v>
+        <v>19420</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>16862</v>
+        <v>16892</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>19598</v>
+        <v>19628</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>32593</v>
+        <v>32653</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>31277</v>
+        <v>31307</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>31628</v>
+        <v>31658</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>32346</v>
+        <v>32376</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>14142</v>
+        <v>14172</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1295,4 +1296,868 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>11873</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+1617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>7608</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8541</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>11904</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>8375</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>20530</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1544</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>16286</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1728</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>9481</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AbdiHyde ID 13496</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>21244</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1824</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>18002</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12167</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>13400</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>6761</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>13222</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>22346</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1229</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MY | Jejaka Tampan</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>3759</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1764</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>12202</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>11836</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+836</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>21336</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+1708</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>34743</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2090</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>32922</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1615</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>33634</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1976</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>530</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>34395</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Tractor Castro V2.0</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>15444</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>20868</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+755</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1353</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Zhogg</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>16085</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1913</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>equin0x</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20060</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Second AangEX</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Yuki</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>3715</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -1322,7 +1322,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-16 13:01:00</t>
+          <t>Timestamp: 2026-07-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -1365,11 +1365,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>11873</v>
+        <v>11933</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+1617</t>
+          <t>+1677</t>
         </is>
       </c>
     </row>
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>8375</v>
+        <v>8400</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1084</t>
+          <t>+1109</t>
         </is>
       </c>
     </row>
@@ -1545,11 +1545,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>16286</v>
+        <v>16316</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+1728</t>
+          <t>+1758</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>21244</v>
+        <v>21274</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+1824</t>
+          <t>+1854</t>
         </is>
       </c>
     </row>
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>6761</v>
+        <v>6791</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+1049</t>
+          <t>+1079</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>21336</v>
+        <v>21396</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+1708</t>
+          <t>+1768</t>
         </is>
       </c>
     </row>
@@ -1875,11 +1875,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>34743</v>
+        <v>34773</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+2090</t>
+          <t>+2120</t>
         </is>
       </c>
     </row>
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>32922</v>
+        <v>32952</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+1615</t>
+          <t>+1645</t>
         </is>
       </c>
     </row>
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>34395</v>
+        <v>34425</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2019</t>
+          <t>+2049</t>
         </is>
       </c>
     </row>
@@ -1965,11 +1965,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>20868</v>
+        <v>21018</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+755</t>
+          <t>+905</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>16085</v>
+        <v>16120</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1913</t>
+          <t>+1948</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2160,4 +2161,868 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>13345</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+1412</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>7608</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8541</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>11904</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>9700</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>22415</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1885</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>17426</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>9481</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AbdiHyde ID 13496</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>22636</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1362</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>19074</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12167</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>13400</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>8073</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>13222</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>23992</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1646</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MY | Jejaka Tampan</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>4909</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1764</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>12212</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>12526</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+690</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>23887</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2491</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>37028</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2255</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35217</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2265</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>35964</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2330</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>730</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+200</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>36668</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2243</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>15464</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>22008</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+990</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+630</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Zhogg</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>17340</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>equin0x</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20590</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+530</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Second AangEX</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Yuki</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>3715</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -2187,7 +2187,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-17 13:01:00</t>
+          <t>Timestamp: 2026-07-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -2230,11 +2230,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>13345</v>
+        <v>13375</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+1412</t>
+          <t>+1442</t>
         </is>
       </c>
     </row>
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>9700</v>
+        <v>9730</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1300</t>
+          <t>+1330</t>
         </is>
       </c>
     </row>
@@ -2455,11 +2455,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+25</t>
         </is>
       </c>
     </row>
@@ -2485,11 +2485,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>22636</v>
+        <v>22666</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+1362</t>
+          <t>+1392</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>8073</v>
+        <v>8103</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+1282</t>
+          <t>+1312</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>37028</v>
+        <v>37058</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+2255</t>
+          <t>+2285</t>
         </is>
       </c>
     </row>
@@ -2755,11 +2755,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>35217</v>
+        <v>35247</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+2265</t>
+          <t>+2295</t>
         </is>
       </c>
     </row>
@@ -2770,11 +2770,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>35964</v>
+        <v>35994</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2330</t>
+          <t>+2360</t>
         </is>
       </c>
     </row>
@@ -2800,11 +2800,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>36668</v>
+        <v>36698</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2243</t>
+          <t>+2273</t>
         </is>
       </c>
     </row>
@@ -2905,11 +2905,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>17340</v>
+        <v>17370</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1250</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -10,6 +10,7 @@
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3025,4 +3026,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>14252</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+877</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>7608</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>12369</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+3828</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>12054</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3723</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+3723</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10591</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+861</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>23851</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1436</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>17551</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+125</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>9631</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AbdiHyde ID 13496</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>24586</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>20435</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1361</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12317</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>13550</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1733</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1723</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1570</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>8646</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>13372</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>-13042</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>25443</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1451</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>MY | Jejaka Tampan</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>4909</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1764</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>12362</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>12837</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25363</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+1476</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>39128</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2070</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37377</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2130</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>38139</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2145</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>730</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>38813</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2115</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>15464</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>22773</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+765</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3414</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1431</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Zhogg</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>17950</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+580</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>equin0x</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>21070</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+480</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Second AangEX</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Yuki</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3715</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -3052,7 +3052,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-18 13:01:00</t>
+          <t>Timestamp: 2026-07-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3095,11 +3095,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>14252</v>
+        <v>14312</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+877</t>
+          <t>+937</t>
         </is>
       </c>
     </row>
@@ -3140,11 +3140,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12054</v>
+        <v>12114</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+150</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -3170,11 +3170,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10591</v>
+        <v>10651</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+861</t>
+          <t>+921</t>
         </is>
       </c>
     </row>
@@ -3185,11 +3185,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23851</v>
+        <v>23971</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+1436</t>
+          <t>+1556</t>
         </is>
       </c>
     </row>
@@ -3275,11 +3275,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>17551</v>
+        <v>17611</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+125</t>
+          <t>+185</t>
         </is>
       </c>
     </row>
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>9631</v>
+        <v>9691</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+150</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -3395,11 +3395,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>13550</v>
+        <v>13610</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+150</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -3455,11 +3455,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>13372</v>
+        <v>13432</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>+150</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -3500,11 +3500,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>-13042</t>
+          <t>-12982</t>
         </is>
       </c>
     </row>
@@ -3575,11 +3575,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>12362</v>
+        <v>12422</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+150</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -3680,11 +3680,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>38813</v>
+        <v>38873</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2115</t>
+          <t>+2175</t>
         </is>
       </c>
     </row>
@@ -3785,11 +3785,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>17950</v>
+        <v>18010</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+580</t>
+          <t>+640</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -11,6 +11,7 @@
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3905,4 +3906,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>19643</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+19643</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>33025</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+18713</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>18995</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+11387</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>27942</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+15573</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>31544</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+19430</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>22079</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+18356</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>28566</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+17915</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>41450</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+17479</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16432</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+16432</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>14746</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+14746</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>15786</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+15785</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>18054</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+18032</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>15650</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+15630</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>35821</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+18210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>33514</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+23823</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>14771</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+14771</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>19829</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+19804</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>15908</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+15908</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AbdiHyde ID 13496</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>45542</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+20956</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>42321</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+21886</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>30400</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+18083</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>32038</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+18428</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>17554</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+15821</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>22276</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+20706</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>24403</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+15757</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>34663</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+34423</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>16341</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+16341</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>18364</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+17888</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21831</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+21591</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>44000</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+18557</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>14632</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+14632</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>MY | Jejaka Tampan</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>17188</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+12279</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>17975</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+16211</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>26966</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+14544</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>29731</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+16894</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>48629</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+23266</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>59474</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+20346</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>59103</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+21726</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>56215</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+18076</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>14308</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+13578</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>62830</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+23957</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>37345</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+21881</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>41051</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+18278</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15813</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+15813</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>21195</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+17781</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Zhogg</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>13859</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+13859</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>18485</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+18485</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>32302</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+14292</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>equin0x</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>18341</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+18341</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>38931</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+17861</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>21992</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+18789</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Second AangEX</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>20172</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+20172</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Yuki</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>20299</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+20299</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>20987</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+17272</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>17528</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+17528</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -3932,7 +3932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-19 13:01:00</t>
+          <t>Timestamp: 2026-07-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>19643</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>+19643</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>33025</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+18713</t>
+          <t>-14312</t>
         </is>
       </c>
     </row>
@@ -3990,11 +3990,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>18995</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+11387</t>
+          <t>-7608</t>
         </is>
       </c>
     </row>
@@ -4005,11 +4005,11 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>27942</v>
+        <v>0</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>+15573</t>
+          <t>-12369</t>
         </is>
       </c>
     </row>
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31544</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+19430</t>
+          <t>-12114</t>
         </is>
       </c>
     </row>
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>22079</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+18356</t>
+          <t>-3723</t>
         </is>
       </c>
     </row>
@@ -4050,11 +4050,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>28566</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+17915</t>
+          <t>-10651</t>
         </is>
       </c>
     </row>
@@ -4065,11 +4065,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>41450</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+17479</t>
+          <t>-23971</t>
         </is>
       </c>
     </row>
@@ -4080,11 +4080,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>16432</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+16432</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4095,11 +4095,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>14746</v>
+        <v>0</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+14746</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15786</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+15785</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -4125,11 +4125,11 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>18054</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+18032</t>
+          <t>-22</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15650</v>
+        <v>0</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>+15630</t>
+          <t>-20</t>
         </is>
       </c>
     </row>
@@ -4155,11 +4155,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>35821</v>
+        <v>0</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+18210</t>
+          <t>-17611</t>
         </is>
       </c>
     </row>
@@ -4170,11 +4170,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>33514</v>
+        <v>0</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+23823</t>
+          <t>-9691</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>14771</v>
+        <v>0</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+14771</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4200,11 +4200,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>19829</v>
+        <v>0</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+19804</t>
+          <t>-25</t>
         </is>
       </c>
     </row>
@@ -4215,11 +4215,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>15908</v>
+        <v>0</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+15908</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45542</v>
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+20956</t>
+          <t>-24586</t>
         </is>
       </c>
     </row>
@@ -4245,11 +4245,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>42321</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+21886</t>
+          <t>-20435</t>
         </is>
       </c>
     </row>
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+18083</t>
+          <t>-12317</t>
         </is>
       </c>
     </row>
@@ -4275,11 +4275,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>32038</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+18428</t>
+          <t>-13610</t>
         </is>
       </c>
     </row>
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>17554</v>
+        <v>0</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+15821</t>
+          <t>-1733</t>
         </is>
       </c>
     </row>
@@ -4305,11 +4305,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>22276</v>
+        <v>0</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+20706</t>
+          <t>-1570</t>
         </is>
       </c>
     </row>
@@ -4320,11 +4320,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>24403</v>
+        <v>0</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+15757</t>
+          <t>-8646</t>
         </is>
       </c>
     </row>
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>34663</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>+34423</t>
+          <t>-240</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>16341</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+16341</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4365,11 +4365,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>18364</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+17888</t>
+          <t>-476</t>
         </is>
       </c>
     </row>
@@ -4380,11 +4380,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>21831</v>
+        <v>0</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+21591</t>
+          <t>-240</t>
         </is>
       </c>
     </row>
@@ -4395,11 +4395,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+18557</t>
+          <t>-25443</t>
         </is>
       </c>
     </row>
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>14632</v>
+        <v>0</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+14632</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4425,11 +4425,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>17188</v>
+        <v>0</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+12279</t>
+          <t>-4909</t>
         </is>
       </c>
     </row>
@@ -4440,11 +4440,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>17975</v>
+        <v>0</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+16211</t>
+          <t>-1764</t>
         </is>
       </c>
     </row>
@@ -4455,11 +4455,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>26966</v>
+        <v>0</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+14544</t>
+          <t>-12422</t>
         </is>
       </c>
     </row>
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>29731</v>
+        <v>0</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+16894</t>
+          <t>-12837</t>
         </is>
       </c>
     </row>
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>48629</v>
+        <v>0</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+23266</t>
+          <t>-25363</t>
         </is>
       </c>
     </row>
@@ -4500,11 +4500,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>59474</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+20346</t>
+          <t>-39128</t>
         </is>
       </c>
     </row>
@@ -4515,11 +4515,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>59103</v>
+        <v>0</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+21726</t>
+          <t>-37377</t>
         </is>
       </c>
     </row>
@@ -4530,11 +4530,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>56215</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+18076</t>
+          <t>-38139</t>
         </is>
       </c>
     </row>
@@ -4545,11 +4545,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>14308</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+13578</t>
+          <t>-730</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>62830</v>
+        <v>0</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+23957</t>
+          <t>-38873</t>
         </is>
       </c>
     </row>
@@ -4575,11 +4575,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>37345</v>
+        <v>0</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+21881</t>
+          <t>-15464</t>
         </is>
       </c>
     </row>
@@ -4590,11 +4590,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>41051</v>
+        <v>0</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+18278</t>
+          <t>-22773</t>
         </is>
       </c>
     </row>
@@ -4605,11 +4605,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>15813</v>
+        <v>0</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+15813</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4620,11 +4620,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>21195</v>
+        <v>0</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+17781</t>
+          <t>-3414</t>
         </is>
       </c>
     </row>
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>13859</v>
+        <v>0</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>+13859</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4650,11 +4650,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>18485</v>
+        <v>0</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+18485</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4665,11 +4665,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>32302</v>
+        <v>0</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+14292</t>
+          <t>-18010</t>
         </is>
       </c>
     </row>
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>18341</v>
+        <v>0</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+18341</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>38931</v>
+        <v>0</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+17861</t>
+          <t>-21070</t>
         </is>
       </c>
     </row>
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>21992</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+18789</t>
+          <t>-3203</t>
         </is>
       </c>
     </row>
@@ -4725,11 +4725,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>20172</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+20172</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>20299</v>
+        <v>0</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+20299</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>20987</v>
+        <v>0</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+17272</t>
+          <t>-3715</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>17528</v>
+        <v>0</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>+17528</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4785,4 +4786,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1196</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+1196</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1044</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1459</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+1459</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+346</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1336</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2965</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2965</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>538</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+538</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+518</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5192</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1922</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+1922</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3423</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+3423</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2635</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+2635</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1089</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1089</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+4645</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2379</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2379</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3056</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+3056</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3057</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3057</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2756</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2756</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1959</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1398</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1398</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1305</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+1305</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1182</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1182</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>equin0x</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2916</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+478</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>3099</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -4812,7 +4812,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-20 13:01:00</t>
+          <t>Timestamp: 2026-07-20 13:31:00</t>
         </is>
       </c>
     </row>
@@ -4855,11 +4855,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1044</v>
+        <v>1074</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+1044</t>
+          <t>+1074</t>
         </is>
       </c>
     </row>
@@ -4870,11 +4870,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1459</v>
+        <v>1485</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+1459</t>
+          <t>+1485</t>
         </is>
       </c>
     </row>
@@ -4945,11 +4945,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1336</v>
+        <v>1366</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+1336</t>
+          <t>+1366</t>
         </is>
       </c>
     </row>
@@ -4960,11 +4960,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2965</v>
+        <v>2995</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+2965</t>
+          <t>+2995</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+538</t>
+          <t>+568</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5192</v>
+        <v>5222</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1922</v>
+        <v>1956</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+1922</t>
+          <t>+1956</t>
         </is>
       </c>
     </row>
@@ -5215,11 +5215,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1089</v>
+        <v>1119</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>+1089</t>
+          <t>+1119</t>
         </is>
       </c>
     </row>
@@ -5365,11 +5365,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+161</t>
         </is>
       </c>
     </row>
@@ -5395,11 +5395,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>3056</v>
+        <v>3086</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+3056</t>
+          <t>+3086</t>
         </is>
       </c>
     </row>
@@ -5410,11 +5410,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>3057</v>
+        <v>3087</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+3057</t>
+          <t>+3087</t>
         </is>
       </c>
     </row>
@@ -5425,11 +5425,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2756</v>
+        <v>2786</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2756</t>
+          <t>+2786</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1398</v>
+        <v>1433</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1398</t>
+          <t>+1433</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2916</v>
+        <v>2946</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>3099</v>
+        <v>3129</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -13,6 +13,7 @@
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5665,4 +5666,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1487</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+291</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+545</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1763</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1763</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4259</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1264</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1078</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+510</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>7246</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2978</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3423</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2645</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+355</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+491</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3565</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3879</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Rian</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>411</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+288</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>4306</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>4317</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1230</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>4071</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1285</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2814</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+855</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+595</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2395</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1493</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>4822</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>905</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+905</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4326</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1197</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -5692,7 +5692,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-21 13:01:00</t>
+          <t>Timestamp: 2026-07-21 13:31:00</t>
         </is>
       </c>
     </row>
@@ -5840,11 +5840,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4259</v>
+        <v>4289</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1264</t>
+          <t>+1294</t>
         </is>
       </c>
     </row>
@@ -5990,11 +5990,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7246</v>
+        <v>7276</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+2024</t>
+          <t>+2054</t>
         </is>
       </c>
     </row>
@@ -6500,11 +6500,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>4326</v>
+        <v>4356</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1197</t>
+          <t>+1227</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6545,4 +6546,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2118</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+631</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3178</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1415</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>5607</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1318</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1078</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>8312</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2978</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3423</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2645</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+445</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3565</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5415</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1536</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Rian</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>888</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+477</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+945</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>6436</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2130</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>6362</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2045</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>6022</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1951</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1834</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>MaJo</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+880</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1493</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>5799</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+977</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1571</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+666</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5262</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+906</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -6572,7 +6572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-22 13:01:00</t>
+          <t>Timestamp: 2026-07-22 13:31:00</t>
         </is>
       </c>
     </row>
@@ -6720,11 +6720,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5607</v>
+        <v>5637</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1318</t>
+          <t>+1348</t>
         </is>
       </c>
     </row>
@@ -7170,11 +7170,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>6436</v>
+        <v>6466</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2130</t>
+          <t>+2160</t>
         </is>
       </c>
     </row>
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>6362</v>
+        <v>6392</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2045</t>
+          <t>+2075</t>
         </is>
       </c>
     </row>
@@ -7200,11 +7200,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>6022</v>
+        <v>6052</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+1951</t>
+          <t>+1981</t>
         </is>
       </c>
     </row>
@@ -7230,11 +7230,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>4648</v>
+        <v>4678</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1834</t>
+          <t>+1864</t>
         </is>
       </c>
     </row>
@@ -7260,11 +7260,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>3395</v>
+        <v>3455</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+1000</t>
+          <t>+1060</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7425,4 +7426,868 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2313</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+195</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4629</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1451</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>7129</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1492</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1078</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+155</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>9209</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+897</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3944</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+966</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3423</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+535</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3565</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>6575</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Rian</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+357</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>2605</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1372</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>8876</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2410</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>8732</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2340</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>8492</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2440</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>6644</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1966</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>4860</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1405</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+700</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1493</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>6139</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+340</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+195</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>5617</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+355</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -7452,7 +7452,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-23 13:01:00</t>
+          <t>Timestamp: 2026-07-23 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7600,11 +7600,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>7129</v>
+        <v>7249</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1492</t>
+          <t>+1612</t>
         </is>
       </c>
     </row>
@@ -7795,11 +7795,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>3944</v>
+        <v>3974</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+966</t>
+          <t>+996</t>
         </is>
       </c>
     </row>
@@ -8035,11 +8035,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>2605</v>
+        <v>2750</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+1372</t>
+          <t>+1517</t>
         </is>
       </c>
     </row>
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>8876</v>
+        <v>8906</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2410</t>
+          <t>+2440</t>
         </is>
       </c>
     </row>
@@ -8065,11 +8065,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>8732</v>
+        <v>8762</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2340</t>
+          <t>+2370</t>
         </is>
       </c>
     </row>
@@ -8080,11 +8080,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>8492</v>
+        <v>8522</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2440</t>
+          <t>+2470</t>
         </is>
       </c>
     </row>
@@ -8110,11 +8110,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>6644</v>
+        <v>6674</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1966</t>
+          <t>+1996</t>
         </is>
       </c>
     </row>
@@ -8200,11 +8200,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>6139</v>
+        <v>6169</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+340</t>
+          <t>+370</t>
         </is>
       </c>
     </row>
@@ -8245,11 +8245,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>5617</v>
+        <v>5647</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+355</t>
+          <t>+385</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -16,6 +16,7 @@
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1305,6 +1306,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2918</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+605</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2835</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+805</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>5534</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+905</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2607</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+701</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8071</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+822</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>665</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+665</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+705</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>9766</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+557</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>5483</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1509</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3573</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2210</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3565</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>7265</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+690</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Rian</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+395</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>4267</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1517</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>10738</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1832</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>10482</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1720</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>10297</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1775</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>7992</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1318</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2476</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+448</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>5813</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+953</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+395</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2146</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+653</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>7723</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1554</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2311</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+545</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>6291</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+644</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -1330,7 +1330,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-24 13:01:00</t>
+          <t>Timestamp: 2026-07-24 13:31:00</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2200</v>
+        <v>2230</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+690</t>
         </is>
       </c>
     </row>
@@ -1388,11 +1388,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2835</v>
+        <v>2865</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+805</t>
+          <t>+835</t>
         </is>
       </c>
     </row>
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2607</v>
+        <v>2637</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+701</t>
+          <t>+731</t>
         </is>
       </c>
     </row>
@@ -1478,11 +1478,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>8071</v>
+        <v>8101</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+822</t>
+          <t>+852</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+665</t>
+          <t>+695</t>
         </is>
       </c>
     </row>
@@ -1583,11 +1583,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1783</v>
+        <v>1813</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+705</t>
+          <t>+735</t>
         </is>
       </c>
     </row>
@@ -1628,11 +1628,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>9766</v>
+        <v>9896</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+557</t>
+          <t>+687</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>5483</v>
+        <v>5513</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1509</t>
+          <t>+1539</t>
         </is>
       </c>
     </row>
@@ -1808,11 +1808,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1830</v>
+        <v>1860</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+780</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>4267</v>
+        <v>4297</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+1517</t>
+          <t>+1547</t>
         </is>
       </c>
     </row>
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>10738</v>
+        <v>10768</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+1832</t>
+          <t>+1862</t>
         </is>
       </c>
     </row>
@@ -1943,11 +1943,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>10482</v>
+        <v>10512</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+1720</t>
+          <t>+1750</t>
         </is>
       </c>
     </row>
@@ -1958,11 +1958,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>10297</v>
+        <v>10327</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+1775</t>
+          <t>+1805</t>
         </is>
       </c>
     </row>
@@ -1988,11 +1988,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>7992</v>
+        <v>8022</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1318</t>
+          <t>+1348</t>
         </is>
       </c>
     </row>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>2146</v>
+        <v>2206</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+653</t>
+          <t>+713</t>
         </is>
       </c>
     </row>
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>7723</v>
+        <v>7753</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1554</t>
+          <t>+1584</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -17,6 +17,7 @@
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2170,6 +2171,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3068</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3388</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+1158</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3525</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6514</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+980</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3242</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+605</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>9511</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+1175</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2983</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+1170</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>10301</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+405</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>7084</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1571</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3858</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+285</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2210</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2785</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2935</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1075</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>8535</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1270</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1815</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+175</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5884</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>12428</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1660</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>12152</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1640</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>11982</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>9606</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1584</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2476</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>7008</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1195</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+460</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3311</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>9324</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1571</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2311</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>7580</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1289</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -2195,7 +2195,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-25 13:01:00</t>
+          <t>Timestamp: 2026-07-25 13:31:00</t>
         </is>
       </c>
     </row>
@@ -2343,11 +2343,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9511</v>
+        <v>9571</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1410</t>
+          <t>+1470</t>
         </is>
       </c>
     </row>
@@ -2538,11 +2538,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>7084</v>
+        <v>7144</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1571</t>
+          <t>+1631</t>
         </is>
       </c>
     </row>
@@ -2553,11 +2553,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>3858</v>
+        <v>3864</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+285</t>
+          <t>+291</t>
         </is>
       </c>
     </row>
@@ -2793,11 +2793,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>12428</v>
+        <v>12488</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+1660</t>
+          <t>+1720</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>12152</v>
+        <v>12212</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+1640</t>
+          <t>+1700</t>
         </is>
       </c>
     </row>
@@ -2823,11 +2823,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>11982</v>
+        <v>12042</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+1655</t>
+          <t>+1715</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>9606</v>
+        <v>9726</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1584</t>
+          <t>+1704</t>
         </is>
       </c>
     </row>
@@ -2943,11 +2943,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>9324</v>
+        <v>9648</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1571</t>
+          <t>+1895</t>
         </is>
       </c>
     </row>
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>7580</v>
+        <v>7640</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1289</t>
+          <t>+1349</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -18,6 +18,7 @@
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3050,6 +3051,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-26 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3068</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>5103</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+1715</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5655</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+2130</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7964</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1450</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4822</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1580</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12391</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>4320</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+2450</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3743</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+760</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>12396</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>10204</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+3060</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5845</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1981</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+850</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4070</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1860</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1710</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>4745</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1810</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10395</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1860</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>603</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2665</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+850</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>7697</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1813</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>16198</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3710</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>15932</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+3720</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>15742</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+3700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>13963</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+4237</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>3436</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>9218</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2210</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1650</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1629</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>14321</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+4673</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1953</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1953</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>12049</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+4409</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -3075,7 +3075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-26 13:01:00</t>
+          <t>Timestamp: 2026-07-26 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3223,11 +3223,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12391</v>
+        <v>12571</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+3000</t>
         </is>
       </c>
     </row>
@@ -3373,11 +3373,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>12396</v>
+        <v>12626</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+2095</t>
+          <t>+2325</t>
         </is>
       </c>
     </row>
@@ -3658,11 +3658,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>7697</v>
+        <v>7817</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+1813</t>
+          <t>+1933</t>
         </is>
       </c>
     </row>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>15742</v>
+        <v>15752</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+3700</t>
+          <t>+3710</t>
         </is>
       </c>
     </row>
@@ -3733,11 +3733,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>13963</v>
+        <v>14023</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+4237</t>
+          <t>+4297</t>
         </is>
       </c>
     </row>
@@ -3793,11 +3793,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1650</v>
+        <v>1770</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1650</t>
+          <t>+1770</t>
         </is>
       </c>
     </row>
@@ -3838,11 +3838,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>1953</v>
+        <v>2019</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1953</t>
+          <t>+2019</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -19,6 +19,7 @@
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3930,6 +3931,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-27 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>8163</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+3060</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>8605</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+2950</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>9104</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7832</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14201</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1630</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6070</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+1750</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+550</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13376</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>10984</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+780</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5845</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4985</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+915</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6545</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>12490</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+351</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>9557</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1740</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>19248</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3050</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>19022</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+3090</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>18792</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+3040</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>16467</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2444</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6470</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3034</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>10898</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>3510</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1740</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>7878</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2938</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>16658</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2337</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2829</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+810</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3571</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>14269</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+2220</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -3955,7 +3955,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-27 13:01:00</t>
+          <t>Timestamp: 2026-07-27 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3998,11 +3998,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8163</v>
+        <v>8223</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+3060</t>
+          <t>+3120</t>
         </is>
       </c>
     </row>
@@ -4013,11 +4013,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>8605</v>
+        <v>8725</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+2950</t>
+          <t>+3070</t>
         </is>
       </c>
     </row>
@@ -4088,11 +4088,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7832</v>
+        <v>7892</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+3010</t>
+          <t>+3070</t>
         </is>
       </c>
     </row>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6070</v>
+        <v>6130</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+1750</t>
+          <t>+1810</t>
         </is>
       </c>
     </row>
@@ -4433,11 +4433,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>6545</v>
+        <v>6605</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+1800</t>
+          <t>+1860</t>
         </is>
       </c>
     </row>
@@ -4583,11 +4583,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>18792</v>
+        <v>18852</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+3040</t>
+          <t>+3100</t>
         </is>
       </c>
     </row>
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>16467</v>
+        <v>16527</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2444</t>
+          <t>+2504</t>
         </is>
       </c>
     </row>
@@ -4628,11 +4628,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>6470</v>
+        <v>6530</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+3034</t>
+          <t>+3094</t>
         </is>
       </c>
     </row>
@@ -4688,11 +4688,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>7878</v>
+        <v>7938</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2938</t>
+          <t>+2998</t>
         </is>
       </c>
     </row>
@@ -4703,11 +4703,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>16658</v>
+        <v>16718</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2337</t>
+          <t>+2397</t>
         </is>
       </c>
     </row>
@@ -4763,11 +4763,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>14269</v>
+        <v>14281</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+2220</t>
+          <t>+2232</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -20,6 +20,7 @@
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4810,6 +4811,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-28 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>8493</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+270</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>9085</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10170</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+327</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14666</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+465</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6265</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+135</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+230</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13409</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>11734</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+750</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5845</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4985</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6921</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+316</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>13364</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+874</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3583</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+567</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>10082</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+525</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>20503</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1255</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>20352</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1330</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>20032</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>18485</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1958</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6920</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>11948</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>4025</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+515</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8058</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>18514</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1796</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2989</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>4206</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+635</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>15794</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1513</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -4835,7 +4835,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-28 13:01:00</t>
+          <t>Timestamp: 2026-07-28 13:31:00</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>13409</v>
+        <v>13439</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+33</t>
+          <t>+63</t>
         </is>
       </c>
     </row>
@@ -5178,11 +5178,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>11734</v>
+        <v>11764</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+750</t>
+          <t>+780</t>
         </is>
       </c>
     </row>
@@ -5493,11 +5493,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>18485</v>
+        <v>18515</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1958</t>
+          <t>+1988</t>
         </is>
       </c>
     </row>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>4025</v>
+        <v>4055</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+515</t>
+          <t>+545</t>
         </is>
       </c>
     </row>
@@ -5583,11 +5583,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>18514</v>
+        <v>18556</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1796</t>
+          <t>+1838</t>
         </is>
       </c>
     </row>
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>15794</v>
+        <v>15824</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1513</t>
+          <t>+1543</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -21,6 +21,7 @@
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5690,6 +5691,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-29 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>8493</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>9085</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>435</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+285</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10590</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16569</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1903</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6265</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13669</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+230</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>12869</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5845</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4985</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2276</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6921</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>14644</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3803</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+220</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>11974</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1892</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>21318</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+815</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>21602</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>20837</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+805</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>20990</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2475</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6920</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>13443</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1495</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>5867</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1812</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8058</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20377</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1821</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3269</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+280</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>4986</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+780</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>17622</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1798</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -5715,7 +5715,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-29 13:01:00</t>
+          <t>Timestamp: 2026-07-29 13:31:00</t>
         </is>
       </c>
     </row>
@@ -6313,11 +6313,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>21318</v>
+        <v>21348</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+815</t>
+          <t>+845</t>
         </is>
       </c>
     </row>
@@ -6343,11 +6343,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>20837</v>
+        <v>20842</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+805</t>
+          <t>+810</t>
         </is>
       </c>
     </row>
@@ -6373,11 +6373,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>20990</v>
+        <v>21020</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2475</t>
+          <t>+2505</t>
         </is>
       </c>
     </row>
@@ -6403,11 +6403,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>13443</v>
+        <v>13473</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+1495</t>
+          <t>+1525</t>
         </is>
       </c>
     </row>
@@ -6433,11 +6433,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>5867</v>
+        <v>5897</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1812</t>
+          <t>+1842</t>
         </is>
       </c>
     </row>
@@ -6463,11 +6463,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>20377</v>
+        <v>20407</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1821</t>
+          <t>+1851</t>
         </is>
       </c>
     </row>
@@ -6523,11 +6523,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>17622</v>
+        <v>17637</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1798</t>
+          <t>+1813</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -22,6 +22,7 @@
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6570,6 +6571,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-30 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9063</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+570</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>9725</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>435</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10966</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+376</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8941</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+722</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>17836</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1267</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6765</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5023</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+730</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1393</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13679</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>13538</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+669</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6535</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+690</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3425</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>5753</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+768</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5135</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-1786</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7617</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+696</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>15629</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+985</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4245</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+442</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>12804</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+830</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>22848</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>23152</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1550</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>22372</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1530</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>22576</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1556</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>7650</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+730</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>14204</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+731</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2605</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+170</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7145</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1248</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8698</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>21642</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1235</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3424</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+155</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>18993</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1356</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -6595,7 +6595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-30 13:01:00</t>
+          <t>Timestamp: 2026-07-30 13:31:00</t>
         </is>
       </c>
     </row>
@@ -6653,11 +6653,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>9725</v>
+        <v>9755</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+640</t>
+          <t>+670</t>
         </is>
       </c>
     </row>
@@ -6758,11 +6758,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6765</v>
+        <v>6795</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>+530</t>
         </is>
       </c>
     </row>
@@ -6938,11 +6938,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>13538</v>
+        <v>13658</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+669</t>
+          <t>+789</t>
         </is>
       </c>
     </row>
@@ -6953,11 +6953,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>6535</v>
+        <v>6595</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+690</t>
+          <t>+750</t>
         </is>
       </c>
     </row>
@@ -6968,11 +6968,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>3425</v>
+        <v>3455</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+690</t>
         </is>
       </c>
     </row>
@@ -7013,11 +7013,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>5753</v>
+        <v>5783</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+768</t>
+          <t>+798</t>
         </is>
       </c>
     </row>
@@ -7028,11 +7028,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>5135</v>
+        <v>5165</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-1786</t>
+          <t>-1756</t>
         </is>
       </c>
     </row>
@@ -7193,11 +7193,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>22848</v>
+        <v>22878</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1530</t>
         </is>
       </c>
     </row>
@@ -7208,11 +7208,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>23152</v>
+        <v>23182</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+1550</t>
+          <t>+1580</t>
         </is>
       </c>
     </row>
@@ -7223,11 +7223,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>22372</v>
+        <v>22402</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+1530</t>
+          <t>+1560</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>22576</v>
+        <v>22598</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1556</t>
+          <t>+1578</t>
         </is>
       </c>
     </row>
@@ -7268,11 +7268,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>7650</v>
+        <v>7680</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+730</t>
+          <t>+760</t>
         </is>
       </c>
     </row>
@@ -7343,11 +7343,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>21642</v>
+        <v>21672</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1235</t>
+          <t>+1265</t>
         </is>
       </c>
     </row>
@@ -7403,11 +7403,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>18993</v>
+        <v>19023</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1356</t>
+          <t>+1386</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -23,6 +23,7 @@
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7450,6 +7451,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-31 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9243</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>9970</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+215</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>435</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>11116</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9096</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+155</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>18670</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+834</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6980</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+185</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5298</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+275</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13709</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>14178</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+520</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6023</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+240</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2242</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>16415</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+786</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4598</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+353</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>13644</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24233</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1355</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>24503</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1321</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>23787</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1385</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23916</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1318</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>7895</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+215</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>14564</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2815</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>8029</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+884</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8883</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+185</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>22080</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+408</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+241</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>20257</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -7475,7 +7475,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-31 13:01:00</t>
+          <t>Timestamp: 2026-07-31 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7518,11 +7518,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>9243</v>
+        <v>9273</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+180</t>
+          <t>+210</t>
         </is>
       </c>
     </row>
@@ -7533,11 +7533,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>9970</v>
+        <v>10000</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+215</t>
+          <t>+245</t>
         </is>
       </c>
     </row>
@@ -7608,11 +7608,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>9096</v>
+        <v>9126</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+155</t>
+          <t>+185</t>
         </is>
       </c>
     </row>
@@ -7623,11 +7623,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>18670</v>
+        <v>18730</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+834</t>
+          <t>+894</t>
         </is>
       </c>
     </row>
@@ -7638,11 +7638,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6980</v>
+        <v>7010</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+185</t>
+          <t>+215</t>
         </is>
       </c>
     </row>
@@ -7728,11 +7728,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>5298</v>
+        <v>5328</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+275</t>
+          <t>+305</t>
         </is>
       </c>
     </row>
@@ -7743,11 +7743,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1603</v>
+        <v>1633</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+210</t>
+          <t>+240</t>
         </is>
       </c>
     </row>
@@ -7893,11 +7893,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>6023</v>
+        <v>6053</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+240</t>
+          <t>+270</t>
         </is>
       </c>
     </row>
@@ -8058,11 +8058,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>13644</v>
+        <v>13674</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+870</t>
         </is>
       </c>
     </row>
@@ -8073,11 +8073,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>24233</v>
+        <v>24263</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+1355</t>
+          <t>+1385</t>
         </is>
       </c>
     </row>
@@ -8088,11 +8088,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>24503</v>
+        <v>24533</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+1321</t>
+          <t>+1351</t>
         </is>
       </c>
     </row>
@@ -8103,11 +8103,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>23787</v>
+        <v>23817</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+1385</t>
+          <t>+1415</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>23916</v>
+        <v>23946</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1318</t>
+          <t>+1348</t>
         </is>
       </c>
     </row>
@@ -8148,11 +8148,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>7895</v>
+        <v>7925</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+215</t>
+          <t>+245</t>
         </is>
       </c>
     </row>
@@ -8193,11 +8193,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>8029</v>
+        <v>8059</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+884</t>
+          <t>+914</t>
         </is>
       </c>
     </row>
@@ -8208,11 +8208,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>8883</v>
+        <v>8913</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+185</t>
+          <t>+215</t>
         </is>
       </c>
     </row>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>20257</v>
+        <v>20287</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1234</t>
+          <t>+1264</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -24,6 +24,7 @@
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8330,6 +8331,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-01 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>435</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>11256</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+185</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>19704</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+974</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13844</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+135</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>14748</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+570</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6113</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>17082</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+667</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4758</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>14644</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+970</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+610</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>25498</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+965</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24432</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+615</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>24932</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+986</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>14864</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2815</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+990</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>23032</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+952</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>4015</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+350</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5496</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+330</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>21275</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+988</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -8355,7 +8355,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-01 13:01:00</t>
+          <t>Timestamp: 2026-08-01 13:31:00</t>
         </is>
       </c>
     </row>
@@ -8923,11 +8923,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>4758</v>
+        <v>4761</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+160</t>
+          <t>+163</t>
         </is>
       </c>
     </row>
@@ -9118,11 +9118,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>4015</v>
+        <v>4245</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+350</t>
+          <t>+580</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -25,6 +25,7 @@
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9210,6 +9211,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-02 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>907</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+472</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>12936</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14097</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+253</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>15783</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6113</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>18930</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1848</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+617</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>5822</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1061</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+366</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>27708</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2210</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24432</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>27004</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2072</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16304</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2815</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24624</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1592</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5796</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>22082</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+807</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+312</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -9235,7 +9235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-02 13:01:00</t>
+          <t>Timestamp: 2026-08-02 13:31:00</t>
         </is>
       </c>
     </row>
@@ -9758,11 +9758,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1650</v>
+        <v>1710</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+617</t>
+          <t>+677</t>
         </is>
       </c>
     </row>
@@ -9803,11 +9803,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>5822</v>
+        <v>6062</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+1061</t>
+          <t>+1301</t>
         </is>
       </c>
     </row>
@@ -9983,11 +9983,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>24624</v>
+        <v>24664</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1592</t>
+          <t>+1632</t>
         </is>
       </c>
     </row>
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>6269</v>
+        <v>6329</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+2024</t>
+          <t>+2084</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -26,6 +26,7 @@
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10954,6 +10955,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-03 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>907</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14016</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14157</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>18102</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2319</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2785</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6113</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20130</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2781</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>6753</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+691</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>29557</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1849</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24432</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>29433</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16904</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2815</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>27097</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2433</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8318</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5816</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23726</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1644</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1929</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1617</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -10979,7 +10979,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-03 13:01:00</t>
+          <t>Timestamp: 2026-08-03 13:31:00</t>
         </is>
       </c>
     </row>
@@ -11322,11 +11322,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>18102</v>
+        <v>18132</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+2319</t>
+          <t>+2349</t>
         </is>
       </c>
     </row>
@@ -11472,11 +11472,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>20130</v>
+        <v>20160</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1230</t>
         </is>
       </c>
     </row>
@@ -11727,11 +11727,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>27097</v>
+        <v>27127</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2433</t>
+          <t>+2463</t>
         </is>
       </c>
     </row>
@@ -11787,11 +11787,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>23726</v>
+        <v>23756</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1644</t>
+          <t>+1674</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -27,6 +27,7 @@
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11834,6 +11835,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-04 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>907</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14616</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14178</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20142</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3085</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6118</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>21150</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+990</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3156</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+375</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1134</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>7494</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+741</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>30646</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1089</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24432</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>31043</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1610</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>17504</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>27187</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>10073</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1755</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5816</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>24044</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+288</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2869</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+940</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -11859,7 +11859,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-04 13:01:00</t>
+          <t>Timestamp: 2026-08-04 13:31:00</t>
         </is>
       </c>
     </row>
@@ -11977,11 +11977,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>14616</v>
+        <v>14918</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+902</t>
         </is>
       </c>
     </row>
@@ -12202,11 +12202,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>20142</v>
+        <v>20182</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+2010</t>
+          <t>+2050</t>
         </is>
       </c>
     </row>
@@ -12517,11 +12517,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>31043</v>
+        <v>31163</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1610</t>
+          <t>+1730</t>
         </is>
       </c>
     </row>
@@ -12622,11 +12622,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>10073</v>
+        <v>10133</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1755</t>
+          <t>+1815</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -28,6 +28,7 @@
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12714,6 +12715,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-05 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1507</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16118</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14178</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>22513</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2331</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3736</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+651</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6118</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>22590</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3156</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1134</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>7794</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24873</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>34379</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+3733</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24432</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1160</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>33797</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2634</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>18404</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>28597</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>12651</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2518</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6167</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>24764</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>4480</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1611</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -12739,7 +12739,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-05 13:01:00</t>
+          <t>Timestamp: 2026-08-05 13:31:00</t>
         </is>
       </c>
     </row>
@@ -13082,11 +13082,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>22513</v>
+        <v>22573</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+2331</t>
+          <t>+2391</t>
         </is>
       </c>
     </row>
@@ -13397,11 +13397,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>33797</v>
+        <v>33857</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2634</t>
+          <t>+2694</t>
         </is>
       </c>
     </row>
@@ -13502,11 +13502,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>12651</v>
+        <v>12711</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+2518</t>
+          <t>+2578</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -29,6 +29,7 @@
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13594,6 +13595,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-06 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16778</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14188</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>25303</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2730</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4036</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BlacKRin O</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6118</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>23750</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1160</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3156</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1144</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>8454</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>27043</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2170</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>37155</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2776</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>26602</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2170</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>2380</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36326</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>8025</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>18404</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>30788</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2191</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>15132</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2421</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6167</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>26744</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6187</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1707</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -13619,7 +13619,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-06 13:01:00</t>
+          <t>Timestamp: 2026-08-06 13:31:00</t>
         </is>
       </c>
     </row>
@@ -14217,11 +14217,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>27043</v>
+        <v>27103</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2170</t>
+          <t>+2230</t>
         </is>
       </c>
     </row>
@@ -14232,11 +14232,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>37155</v>
+        <v>37215</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2776</t>
+          <t>+2836</t>
         </is>
       </c>
     </row>
@@ -14247,11 +14247,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>26602</v>
+        <v>26662</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2170</t>
+          <t>+2230</t>
         </is>
       </c>
     </row>
@@ -14262,11 +14262,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2380</v>
+        <v>2440</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+1220</t>
+          <t>+1280</t>
         </is>
       </c>
     </row>
@@ -14277,11 +14277,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>36326</v>
+        <v>36386</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2469</t>
+          <t>+2529</t>
         </is>
       </c>
     </row>
@@ -14367,11 +14367,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>30788</v>
+        <v>30848</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2191</t>
+          <t>+2251</t>
         </is>
       </c>
     </row>
@@ -14427,11 +14427,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>26744</v>
+        <v>26804</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1980</t>
+          <t>+2040</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -30,6 +30,7 @@
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14474,6 +14475,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-07 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2210</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+403</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>17978</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14188</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>27211</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1908</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4336</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>645</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+320</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>24490</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>3466</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1144</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>9066</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+612</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>29923</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>40035</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>29482</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>39026</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2640</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>8025</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18704</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>33587</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2739</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>18012</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6167</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>29534</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+2730</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6997</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+810</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -14499,7 +14499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-07 13:01:00</t>
+          <t>Timestamp: 2026-08-07 13:31:00</t>
         </is>
       </c>
     </row>
@@ -14617,11 +14617,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>17978</v>
+        <v>18278</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1500</t>
         </is>
       </c>
     </row>
@@ -15082,11 +15082,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>29923</v>
+        <v>29983</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -15097,11 +15097,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>40035</v>
+        <v>40095</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -15112,11 +15112,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>29482</v>
+        <v>29542</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -15142,11 +15142,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>39026</v>
+        <v>39086</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2640</t>
+          <t>+2700</t>
         </is>
       </c>
     </row>
@@ -15247,11 +15247,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>33587</v>
+        <v>33647</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2739</t>
+          <t>+2799</t>
         </is>
       </c>
     </row>
@@ -15262,11 +15262,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>18012</v>
+        <v>18072</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+2880</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -15307,11 +15307,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>29534</v>
+        <v>29594</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+2730</t>
+          <t>+2790</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -31,6 +31,7 @@
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15354,6 +15355,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-08 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>9333</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>10090</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3110</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+228</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>19580</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9311</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>5418</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14188</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>29851</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2640</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3665</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4506</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+170</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>5375</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-2452</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Mantul.io</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>945</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>7827</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>25630</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>4471</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+170</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>9617</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+551</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>32803</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>42915</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>32362</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>41681</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2595</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>8025</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18714</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>9049</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8973</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>36359</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2712</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>19944</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1872</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6167</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>32360</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>8677</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -15379,7 +15379,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-08 13:01:00</t>
+          <t>Timestamp: 2026-08-08 13:31:00</t>
         </is>
       </c>
     </row>
@@ -15677,11 +15677,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>14188</v>
+        <v>14468</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+280</t>
         </is>
       </c>
     </row>
@@ -15962,11 +15962,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>32803</v>
+        <v>32923</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -15977,11 +15977,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>42915</v>
+        <v>43035</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -15992,11 +15992,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>32362</v>
+        <v>32482</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -16022,11 +16022,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>41681</v>
+        <v>41801</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2595</t>
+          <t>+2715</t>
         </is>
       </c>
     </row>
@@ -16127,11 +16127,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>36359</v>
+        <v>36479</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2712</t>
+          <t>+2832</t>
         </is>
       </c>
     </row>
@@ -16142,11 +16142,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>19944</v>
+        <v>20064</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1872</t>
+          <t>+1992</t>
         </is>
       </c>
     </row>
@@ -16187,11 +16187,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>32360</v>
+        <v>32480</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+2766</t>
+          <t>+2886</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -32,6 +32,7 @@
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16234,6 +16235,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-09 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>26348</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+22980</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Daizen Uchiha</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>26672</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+16582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>28174</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+25064</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>18807</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+17741</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>18989</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+18761</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>39701</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+20121</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>28673</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+19362</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>39882</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+19868</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>25053</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+18043</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6771</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+6771</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>8730</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+8730</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>24485</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+24437</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>8766</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+8766</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>17503</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+17273</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>12271</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+6853</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>19325</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+17692</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6530</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+6530</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>34817</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+20349</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>8884</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+8884</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>6379</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+6379</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>51889</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+22038</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>24737</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+17932</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>35002</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+31337</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>18438</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+18438</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>20254</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+15748</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>36062</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+28235</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>19603</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+18658</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>39305</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+31478</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CatDile</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>24152</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>43248</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+17618</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>10901</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+10901</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>27372</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+22901</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>18677</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+18502</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>19764</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+18450</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>30040</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+20423</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>33918</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+18908</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>55335</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+22412</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>65420</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+22385</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>55148</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+22666</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>10691</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+8131</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>64699</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+22898</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>25381</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+17356</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>33514</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+14800</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18522</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+15167</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>11279</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2230</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>19812</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+19812</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>17547</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+8574</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>55307</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+18828</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>39924</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+19860</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>25164</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+18997</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>17257</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+16749</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>50466</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+17986</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>YuPaNkI</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>8964</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>25511</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+16834</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>19335</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+19335</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -16259,7 +16259,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-09 13:01:00</t>
+          <t>Timestamp: 2026-08-09 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -33,6 +33,7 @@
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17114,6 +17115,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-10 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>-26348</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>-28174</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>-18807</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>-18989</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-38777</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>-28673</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-39882</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>-25053</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-6771</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Exe™</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>-8730</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>-24485</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>-8766</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>-17503</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>-12271</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>-19325</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>-6530</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>-34817</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>-8884</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>-6379</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>-51889</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>-24737</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>-35002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>-18438</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>984</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>-19270</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>-39305</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-19603</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-39305</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CatDile</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>-23652</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>-43184</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>-10901</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-27372</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>-18677</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>-19764</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>-30039</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>-33918</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>-55335</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>-65420</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>-55148</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>-10691</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>-63571</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>-25381</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>-33514</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-18522</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>-11279</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>-19812</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>-17547</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>-54588</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1073</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>-38851</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>848</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>-24316</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>-17257</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>918</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>-49548</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>YuPaNkI</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>-8964</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>-25511</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>-19335</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -17139,7 +17139,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-10 13:01:00</t>
+          <t>Timestamp: 2026-08-10 13:31:00</t>
         </is>
       </c>
     </row>
@@ -17767,11 +17767,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1128</v>
+        <v>1278</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>-63571</t>
+          <t>-63421</t>
         </is>
       </c>
     </row>
@@ -17872,11 +17872,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>719</v>
+        <v>797</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>-54588</t>
+          <t>-54510</t>
         </is>
       </c>
     </row>
@@ -17887,11 +17887,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>1073</v>
+        <v>1223</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>-38851</t>
+          <t>-38701</t>
         </is>
       </c>
     </row>
@@ -17902,11 +17902,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>848</v>
+        <v>998</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>-24316</t>
+          <t>-24166</t>
         </is>
       </c>
     </row>
@@ -17932,11 +17932,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>-49548</t>
+          <t>-49542</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -34,6 +34,7 @@
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17994,6 +17995,855 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-11 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+128</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3011</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+2087</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1884</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+75</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>744</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+743</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+3580</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1892</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+1892</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3636</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+3636</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>5022</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3744</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Nami</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2286</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+1489</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>2470</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1247</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2838</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1840</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>763</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+763</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2277</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1353</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>YuPaNkI</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>3115</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -18019,7 +18019,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-11 13:01:00</t>
+          <t>Timestamp: 2026-08-11 13:31:00</t>
         </is>
       </c>
     </row>
@@ -18527,11 +18527,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>744</v>
+        <v>1044</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+743</t>
+          <t>+1043</t>
         </is>
       </c>
     </row>
@@ -18557,11 +18557,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>3580</v>
+        <v>3640</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+3580</t>
+          <t>+3640</t>
         </is>
       </c>
     </row>
@@ -18572,11 +18572,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1892</v>
+        <v>1952</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+1892</t>
+          <t>+1952</t>
         </is>
       </c>
     </row>
@@ -18587,11 +18587,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>3636</v>
+        <v>3696</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+3636</t>
+          <t>+3696</t>
         </is>
       </c>
     </row>
@@ -18617,11 +18617,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>5022</v>
+        <v>5082</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+3744</t>
+          <t>+3804</t>
         </is>
       </c>
     </row>
@@ -18722,11 +18722,11 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>2286</v>
+        <v>2346</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>+1489</t>
+          <t>+1549</t>
         </is>
       </c>
     </row>
@@ -18782,11 +18782,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2277</v>
+        <v>2337</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1353</t>
+          <t>+1413</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -35,6 +35,7 @@
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18844,6 +18845,840 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-12 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4571</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1560</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>560</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+560</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2604</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+780</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3372</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1424</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1984</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+940</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>6742</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+3102</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>4438</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2486</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>6918</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+3222</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MY | Kosuke Ueki</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>8191</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3109</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>5629</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+3283</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2470</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>4122</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>763</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>5603</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3266</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>YuPaNkI</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5742</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2627</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -18869,7 +18869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-12 13:01:00</t>
+          <t>Timestamp: 2026-08-12 13:31:00</t>
         </is>
       </c>
     </row>
@@ -19422,11 +19422,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>4438</v>
+        <v>4498</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+2486</t>
+          <t>+2546</t>
         </is>
       </c>
     </row>
@@ -19467,11 +19467,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>8191</v>
+        <v>8251</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+3109</t>
+          <t>+3169</t>
         </is>
       </c>
     </row>
@@ -19557,11 +19557,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>5629</v>
+        <v>5689</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+3283</t>
+          <t>+3343</t>
         </is>
       </c>
     </row>
@@ -19617,11 +19617,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>5603</v>
+        <v>5663</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3266</t>
+          <t>+3326</t>
         </is>
       </c>
     </row>
@@ -19647,11 +19647,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>5742</v>
+        <v>5802</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+2627</t>
+          <t>+2687</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -36,6 +36,7 @@
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-08-14" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20543,6 +20544,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-14 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6493</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1922</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1105</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+210</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2988</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+384</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>5188</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1816</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+721</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>11910</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+5168</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>9430</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+4932</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>12090</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+5172</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>13033</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+4782</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>10645</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4956</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>6626</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2504</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1479</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>10724</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5061</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>9685</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+3883</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -20568,7 +20568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-14 13:01:00</t>
+          <t>Timestamp: 2026-08-14 13:31:00</t>
         </is>
       </c>
     </row>
@@ -20911,11 +20911,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1200</v>
+        <v>1260</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1260</t>
         </is>
       </c>
     </row>
@@ -21151,11 +21151,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>11910</v>
+        <v>11970</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+5168</t>
+          <t>+5228</t>
         </is>
       </c>
     </row>
@@ -21166,11 +21166,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>9430</v>
+        <v>9490</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+4932</t>
+          <t>+4992</t>
         </is>
       </c>
     </row>
@@ -21181,11 +21181,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>12090</v>
+        <v>12150</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+5172</t>
+          <t>+5232</t>
         </is>
       </c>
     </row>
@@ -21211,11 +21211,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>13033</v>
+        <v>13093</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+4782</t>
+          <t>+4842</t>
         </is>
       </c>
     </row>
@@ -21301,11 +21301,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>10645</v>
+        <v>10705</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4956</t>
+          <t>+5016</t>
         </is>
       </c>
     </row>
@@ -21316,11 +21316,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2780</v>
+        <v>3030</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+560</t>
         </is>
       </c>
     </row>
@@ -21361,11 +21361,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>10724</v>
+        <v>10784</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+5061</t>
+          <t>+5121</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -37,6 +37,7 @@
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-08-14" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-08-15" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21408,6 +21409,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-15 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1208</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7813</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2335</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1230</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>770</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1620</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3288</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+350</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6210</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3045</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+340</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>14790</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>12310</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>14970</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>15859</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>12559</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1854</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>5690</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2660</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>7226</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>13442</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2658</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>9985</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -21433,7 +21433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-15 13:01:00</t>
+          <t>Timestamp: 2026-08-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -21581,11 +21581,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2335</v>
+        <v>2455</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1230</t>
+          <t>+1350</t>
         </is>
       </c>
     </row>
@@ -21776,11 +21776,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>2880</v>
+        <v>3000</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1620</t>
+          <t>+1740</t>
         </is>
       </c>
     </row>
@@ -22001,11 +22001,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>960</v>
+        <v>1080</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+960</t>
+          <t>+1080</t>
         </is>
       </c>
     </row>
@@ -22016,11 +22016,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>14790</v>
+        <v>14910</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -22031,11 +22031,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>12310</v>
+        <v>12430</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -22046,11 +22046,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>14970</v>
+        <v>15090</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -22076,11 +22076,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>15859</v>
+        <v>15979</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2766</t>
+          <t>+2886</t>
         </is>
       </c>
     </row>
@@ -22166,11 +22166,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>12559</v>
+        <v>12679</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1854</t>
+          <t>+1974</t>
         </is>
       </c>
     </row>
@@ -22226,11 +22226,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>13442</v>
+        <v>13562</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2658</t>
+          <t>+2778</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -38,6 +38,7 @@
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-08-14" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-08-15" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-08-16" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22273,6 +22274,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2648</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>11341</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+3528</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8231</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+5776</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10794</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+10024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>7095</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+4095</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3288</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>8274</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2064</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3045</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>7163</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+6083</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>22190</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+7280</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>19718</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+7288</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>22362</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+7272</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>22809</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+6830</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>19493</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+6814</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>12629</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+6939</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8262</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>20664</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+7102</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>13989</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -22298,7 +22298,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-16 13:01:00</t>
+          <t>Timestamp: 2026-08-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -22881,11 +22881,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>22190</v>
+        <v>22358</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+7280</t>
+          <t>+7448</t>
         </is>
       </c>
     </row>
@@ -22896,11 +22896,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>19718</v>
+        <v>19886</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+7288</t>
+          <t>+7456</t>
         </is>
       </c>
     </row>
@@ -22911,11 +22911,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>22362</v>
+        <v>22530</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+7272</t>
+          <t>+7440</t>
         </is>
       </c>
     </row>
@@ -22941,11 +22941,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>22809</v>
+        <v>22977</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+6830</t>
+          <t>+6998</t>
         </is>
       </c>
     </row>
@@ -23031,11 +23031,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>19493</v>
+        <v>19661</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+6814</t>
+          <t>+6982</t>
         </is>
       </c>
     </row>
@@ -23091,11 +23091,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>20664</v>
+        <v>20832</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+7102</t>
+          <t>+7270</t>
         </is>
       </c>
     </row>
@@ -23106,11 +23106,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>13989</v>
+        <v>14157</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+4004</t>
+          <t>+4172</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -39,6 +39,7 @@
     <sheet name="2026-08-14" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-08-15" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-08-16" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-08-17" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23138,6 +23139,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>5989</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+3341</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14701</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+3360</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12218</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+3987</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10794</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>9280</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2185</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3288</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+818</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>10742</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2468</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ninja II</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3045</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>13235</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+6072</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>28714</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+6356</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26170</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+6284</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>28782</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+6252</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>29689</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+6712</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>26026</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+6365</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>17387</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+4758</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8262</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>27076</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+6244</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>18044</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+3887</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -23163,7 +23163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-17 13:01:00</t>
+          <t>Timestamp: 2026-08-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -23731,11 +23731,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>13235</v>
+        <v>13295</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+6072</t>
+          <t>+6132</t>
         </is>
       </c>
     </row>
@@ -23746,11 +23746,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>28714</v>
+        <v>28774</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+6356</t>
+          <t>+6416</t>
         </is>
       </c>
     </row>
@@ -23761,11 +23761,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>26170</v>
+        <v>26230</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+6284</t>
+          <t>+6344</t>
         </is>
       </c>
     </row>
@@ -23776,11 +23776,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>28782</v>
+        <v>28842</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+6252</t>
+          <t>+6312</t>
         </is>
       </c>
     </row>
@@ -23806,11 +23806,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>29689</v>
+        <v>29749</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+6712</t>
+          <t>+6772</t>
         </is>
       </c>
     </row>
@@ -23896,11 +23896,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>26026</v>
+        <v>26086</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+6365</t>
+          <t>+6425</t>
         </is>
       </c>
     </row>
@@ -23956,11 +23956,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>27076</v>
+        <v>27136</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+6244</t>
+          <t>+6304</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -40,6 +40,7 @@
     <sheet name="2026-08-15" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-08-16" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-08-17" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-08-18" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24003,6 +24004,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7369</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1380</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14701</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12218</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10794</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>11144</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1864</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3579</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+291</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>12243</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3569</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+524</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15062</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>31768</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2994</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>29192</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2962</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>31824</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2982</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2851</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>29022</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2936</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>18527</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8262</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>30347</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3211</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>19706</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1662</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -24028,7 +24028,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-18 13:01:00</t>
+          <t>Timestamp: 2026-08-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -24371,11 +24371,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>11144</v>
+        <v>11204</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1864</t>
+          <t>+1924</t>
         </is>
       </c>
     </row>
@@ -24761,11 +24761,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>29022</v>
+        <v>29082</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2936</t>
+          <t>+2996</t>
         </is>
       </c>
     </row>
@@ -24821,11 +24821,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>30347</v>
+        <v>30407</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+3211</t>
+          <t>+3271</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -41,6 +41,7 @@
     <sheet name="2026-08-16" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-08-17" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-08-18" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026-08-19" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24868,6 +24869,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7399</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14701</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12218</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10804</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>13096</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+1892</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+253</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3579</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3448</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>13275</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>4158</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+589</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15062</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>34882</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+3114</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>32294</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+3102</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>34930</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+3106</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>35775</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+3175</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>31914</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2832</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>21749</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3222</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>9282</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>33695</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3288</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>21698</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1992</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -24893,7 +24893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-19 13:01:00</t>
+          <t>Timestamp: 2026-08-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -25236,11 +25236,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>13096</v>
+        <v>13156</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+1892</t>
+          <t>+1952</t>
         </is>
       </c>
     </row>
@@ -25476,11 +25476,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>34882</v>
+        <v>34942</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+3114</t>
+          <t>+3174</t>
         </is>
       </c>
     </row>
@@ -25491,11 +25491,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>32294</v>
+        <v>32354</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+3102</t>
+          <t>+3162</t>
         </is>
       </c>
     </row>
@@ -25506,11 +25506,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>34930</v>
+        <v>34990</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+3106</t>
+          <t>+3166</t>
         </is>
       </c>
     </row>
@@ -25536,11 +25536,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>35775</v>
+        <v>35835</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+3175</t>
+          <t>+3235</t>
         </is>
       </c>
     </row>
@@ -25641,11 +25641,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>21749</v>
+        <v>21809</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3222</t>
+          <t>+3282</t>
         </is>
       </c>
     </row>
@@ -25686,11 +25686,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>33695</v>
+        <v>33755</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+3288</t>
+          <t>+3348</t>
         </is>
       </c>
     </row>
@@ -25701,11 +25701,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>21698</v>
+        <v>21998</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1992</t>
+          <t>+2292</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -42,6 +42,7 @@
     <sheet name="2026-08-17" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-08-18" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-08-19" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="2026-08-20" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25733,6 +25734,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7413</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>15313</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+612</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hydra anbu™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12768</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+550</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Valter</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10804</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>15503</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+2347</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3947</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+368</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3748</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>14300</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>4458</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>15062</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37047</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2105</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>34529</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2175</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2109</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>38617</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2782</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ANBU | HERO NICO 15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>33109</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1195</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24023</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2214</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>9582</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>36027</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2272</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23357</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -25758,7 +25758,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-20 13:01:00</t>
+          <t>Timestamp: 2026-08-20 13:31:00</t>
         </is>
       </c>
     </row>
@@ -26401,11 +26401,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>38617</v>
+        <v>38677</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2782</t>
+          <t>+2842</t>
         </is>
       </c>
     </row>
@@ -26506,11 +26506,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>24023</v>
+        <v>24083</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2214</t>
+          <t>+2274</t>
         </is>
       </c>
     </row>
@@ -26566,11 +26566,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>23357</v>
+        <v>23417</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1359</t>
+          <t>+1419</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -43,6 +43,7 @@
     <sheet name="2026-08-18" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-08-19" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-08-20" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="2026-08-21" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26598,6 +26599,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7413</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16088</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+775</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>14585</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1817</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>10804</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>16571</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3947</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3748</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15731</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1431</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>4458</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>15704</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+642</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>38205</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1158</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>35741</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1212</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>38545</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1446</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>41443</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>35698</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2589</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>26784</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2701</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>9582</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>36027</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>24797</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1380</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -26623,7 +26623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-21 13:01:00</t>
+          <t>Timestamp: 2026-08-21 13:31:00</t>
         </is>
       </c>
     </row>
@@ -26756,11 +26756,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>14585</v>
+        <v>14591</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+1817</t>
+          <t>+1823</t>
         </is>
       </c>
     </row>
@@ -27176,11 +27176,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>15704</v>
+        <v>15824</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+642</t>
+          <t>+762</t>
         </is>
       </c>
     </row>
@@ -27251,11 +27251,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>41443</v>
+        <v>41503</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2766</t>
+          <t>+2826</t>
         </is>
       </c>
     </row>
@@ -27356,11 +27356,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>35698</v>
+        <v>35758</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2589</t>
+          <t>+2649</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -44,6 +44,7 @@
     <sheet name="2026-08-19" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-08-20" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-08-21" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="2026-08-22" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27478,6 +27479,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7413</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16808</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>16291</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>The ProfessorX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>10804</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>17831</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1091</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3947</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4048</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>16651</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+920</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>4758</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>17624</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>40006</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1801</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37542</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1801</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>40346</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1801</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>44323</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>912</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+612</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>37375</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1617</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>28625</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1841</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>9582</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>36027</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1374</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>26627</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1830</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -27503,7 +27503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-22 13:01:00</t>
+          <t>Timestamp: 2026-08-22 13:31:00</t>
         </is>
       </c>
     </row>
@@ -27636,11 +27636,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>16291</v>
+        <v>16411</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+1700</t>
+          <t>+1820</t>
         </is>
       </c>
     </row>
@@ -28056,11 +28056,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>17624</v>
+        <v>17744</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+1800</t>
+          <t>+1920</t>
         </is>
       </c>
     </row>
@@ -28131,11 +28131,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>44323</v>
+        <v>44443</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -28236,11 +28236,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>37375</v>
+        <v>37975</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1617</t>
+          <t>+2217</t>
         </is>
       </c>
     </row>
@@ -28296,11 +28296,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>36027</v>
+        <v>36627</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+600</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -45,6 +45,7 @@
     <sheet name="2026-08-20" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-08-21" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-08-22" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="2026-08-23" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28358,6 +28359,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>9617</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+2204</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>17408</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>21773</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+5362</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Toka Senju™</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1901</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1901</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Seijuu X</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>15504</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>22031</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+4200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4975</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+3884</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4547</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4048</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>19133</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+2482</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>4758</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>23207</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+5463</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>44466</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+4460</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>42002</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+4460</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>44806</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+4460</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>49969</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+5526</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+4800</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>6374</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+5462</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>40255</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2280</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>32029</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3404</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>10202</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+620</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2242</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>42071</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5444</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>26627</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -28383,7 +28383,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-23 13:01:00</t>
+          <t>Timestamp: 2026-08-23 13:31:00</t>
         </is>
       </c>
     </row>
@@ -28516,11 +28516,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>21773</v>
+        <v>22133</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+5362</t>
+          <t>+5722</t>
         </is>
       </c>
     </row>
@@ -28696,11 +28696,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>22031</v>
+        <v>22151</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+4200</t>
+          <t>+4320</t>
         </is>
       </c>
     </row>
@@ -28936,11 +28936,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>23207</v>
+        <v>23327</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+5463</t>
+          <t>+5583</t>
         </is>
       </c>
     </row>
@@ -28951,11 +28951,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>44466</v>
+        <v>44586</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+4460</t>
+          <t>+4580</t>
         </is>
       </c>
     </row>
@@ -28981,11 +28981,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>44806</v>
+        <v>44926</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+4460</t>
+          <t>+4580</t>
         </is>
       </c>
     </row>
@@ -29011,11 +29011,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>49969</v>
+        <v>50089</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+5526</t>
+          <t>+5646</t>
         </is>
       </c>
     </row>
@@ -29041,11 +29041,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>4800</v>
+        <v>5160</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+4800</t>
+          <t>+5160</t>
         </is>
       </c>
     </row>
@@ -29176,11 +29176,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>42071</v>
+        <v>42311</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+5444</t>
+          <t>+5684</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -46,6 +46,7 @@
     <sheet name="2026-08-21" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-08-22" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-08-23" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="2026-08-24" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30117,6 +30118,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>11979</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+2362</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>19188</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1780</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>27539</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+5406</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2501</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>16885</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>24551</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2400</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>8137</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+3162</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5591</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>22634</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3501</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TipeneMartipene</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity Jr.</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>5358</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>26832</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+3505</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>49886</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+5300</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>47302</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+5300</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>50226</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+5300</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>55729</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+5640</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>10629</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+5469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>12045</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+5671</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>40855</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>37252</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+5223</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>13922</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+3720</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>43062</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+751</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4266</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+644</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -30142,7 +30142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-24 13:01:00</t>
+          <t>Timestamp: 2026-08-24 13:31:00</t>
         </is>
       </c>
     </row>
@@ -30260,11 +30260,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>27539</v>
+        <v>27659</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+5406</t>
+          <t>+5526</t>
         </is>
       </c>
     </row>
@@ -30365,7 +30365,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>16885</v>
+        <v>16915</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -30680,11 +30680,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>26832</v>
+        <v>26952</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+3505</t>
+          <t>+3625</t>
         </is>
       </c>
     </row>
@@ -30695,11 +30695,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>49886</v>
+        <v>49946</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+5300</t>
+          <t>+5360</t>
         </is>
       </c>
     </row>
@@ -30755,11 +30755,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>55729</v>
+        <v>55789</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+5640</t>
+          <t>+5700</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -47,6 +47,7 @@
     <sheet name="2026-08-22" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-08-23" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-08-24" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="2026-08-25" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30997,6 +30998,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12039</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>20099</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+911</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>30239</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2580</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2529</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>18588</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1673</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>25511</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>9514</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1377</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5591</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>23656</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TipeneMartipene</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity Jr.</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>5778</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>29745</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2793</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>52766</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>50182</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>53106</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>58519</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2730</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>12537</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1908</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>13821</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1776</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>41326</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+471</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>39755</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2503</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>14522</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>44748</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1686</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5283</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -31022,7 +31022,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-25 13:01:00</t>
+          <t>Timestamp: 2026-08-25 13:31:00</t>
         </is>
       </c>
     </row>
@@ -31140,11 +31140,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>30239</v>
+        <v>30489</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+2580</t>
+          <t>+2830</t>
         </is>
       </c>
     </row>
@@ -31245,11 +31245,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>18588</v>
+        <v>18888</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+1673</t>
+          <t>+1973</t>
         </is>
       </c>
     </row>
@@ -31545,11 +31545,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>5778</v>
+        <v>6078</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+420</t>
+          <t>+720</t>
         </is>
       </c>
     </row>
@@ -31560,11 +31560,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>29745</v>
+        <v>29805</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+2793</t>
+          <t>+2853</t>
         </is>
       </c>
     </row>
@@ -31605,11 +31605,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>53106</v>
+        <v>53166</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2880</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -31635,11 +31635,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>58519</v>
+        <v>58579</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2730</t>
+          <t>+2790</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -48,6 +48,7 @@
     <sheet name="2026-08-23" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-08-24" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-25" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="2026-08-26" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31877,6 +31878,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-26 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12069</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>20990</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+891</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>32148</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1659</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2529</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>20695</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1807</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>26951</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>11125</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5882</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+291</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4648</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>25900</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2244</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TipeneMartipene</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity Jr.</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>6238</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>32556</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2751</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>55006</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2240</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>52482</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2300</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>55406</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2240</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>61267</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2688</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>15330</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2793</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>16575</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2754</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>42466</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>42065</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>15182</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>45828</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>6126</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+843</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -31884,7 +31884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -31902,7 +31902,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-26 13:01:00</t>
+          <t>Timestamp: 2026-08-26 13:31:00</t>
         </is>
       </c>
     </row>
@@ -32020,11 +32020,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>32148</v>
+        <v>32398</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1659</t>
+          <t>+1909</t>
         </is>
       </c>
     </row>
@@ -32121,26 +32121,26 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>ProfessorX ?</t>
+          <t>KataChi</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>20695</v>
+        <v>0</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+1807</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>KataChi</t>
+          <t>Dmtr</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -32151,11 +32151,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Dmtr</t>
+          <t>Scarlet</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -32166,71 +32166,71 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Scarlet</t>
+          <t>Torune | Anbu</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0</v>
+        <v>26951</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1440</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Torune | Anbu</t>
+          <t>San Pate Té</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>26951</v>
+        <v>0</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1440</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>San Pate Té</t>
+          <t>A K A G A M I</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0</v>
+        <v>11125</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>A K A G A M I</t>
+          <t>Sabrina Carpenter</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>11125</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Sabrina Carpenter</t>
+          <t>HASHIRAMA</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -32241,11 +32241,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>HASHIRAMA</t>
+          <t>BlacKaguya Ô</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>563</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -32256,41 +32256,41 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>BlacKaguya Ô</t>
+          <t>Kiroi Senko</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>30</v>
+        <v>5882</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+291</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Kiroi Senko</t>
+          <t>NPC | SNOOPY</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>5882</v>
+        <v>0</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+291</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>NPC | SNOOPY</t>
+          <t>BEBO</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>4648</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -32301,11 +32301,11 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>BEBO</t>
+          <t>NPC | SNOOPY</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>4648</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -32316,41 +32316,41 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>NPC | SNOOPY</t>
+          <t>S3YL3</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2244</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>S3YL3</t>
+          <t>YinRaku ™</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>25900</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2244</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>YinRaku ™</t>
+          <t>TipeneMartipene</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -32361,26 +32361,26 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>TipeneMartipene</t>
+          <t>Mr.Shelby</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Izx Infernity Jr.</t>
+          <t>BlacKObito O</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -32391,142 +32391,142 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>BlacKObito O</t>
+          <t>FEARLESS</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>FEARLESS</t>
+          <t>™$£iko™°</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>40</v>
+        <v>6238</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+160</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>™$£iko™°</t>
+          <t>zDexTerx</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>6238</v>
+        <v>32556</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+160</t>
+          <t>+2751</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>zDexTerx</t>
+          <t>Archaic</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>32556</v>
+        <v>55006</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+2751</t>
+          <t>+2240</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Archaic</t>
+          <t>Nixervo</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>55006</v>
+        <v>52482</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+2240</t>
+          <t>+2300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Nixervo</t>
+          <t>Abyssteroth</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>52482</v>
+        <v>55406</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+2300</t>
+          <t>+2240</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Abyssteroth</t>
+          <t>Floid</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>55406</v>
+        <v>0</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2240</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Floid</t>
+          <t>Kojima</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0</v>
+        <v>61387</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2808</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Kojima</t>
+          <t>SharinganKniGhT</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>61267</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2688</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>SharinganKniGhT</t>
+          <t>Wampiptipayb.</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -32541,37 +32541,37 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Wampiptipayb.</t>
+          <t>BlacKenzie O</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0</v>
+        <v>15330</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2793</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>BlacKenzie O</t>
+          <t>Ryujin 2ND</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>15330</v>
+        <v>0</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2793</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Ryujin 2ND</t>
+          <t>SHINRAIN ZENIN®</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -32586,7 +32586,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>SHINRAIN ZENIN®</t>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -32601,148 +32601,133 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UJKU SHIJAKUT </t>
+          <t>BlacKEucresia Ó</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0</v>
+        <v>16614</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2793</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>BlacKEucresia Ó</t>
+          <t>RS | Oboy Max</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>16575</v>
+        <v>42466</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+2754</t>
+          <t>+1140</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>RS | Oboy Max</t>
+          <t>a_t_h_a_l_i_a</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>42466</v>
+        <v>42065</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1140</t>
+          <t>+2310</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>a_t_h_a_l_i_a</t>
+          <t>SB | PapiiChan</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>42065</v>
+        <v>15182</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2310</t>
+          <t>+660</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SB | PapiiChan</t>
+          <t>RS | Oboy Lite</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>15182</v>
+        <v>45828</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+660</t>
+          <t>+1080</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>RS | Oboy Lite</t>
+          <t>[R23] Hound †</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>45828</v>
+        <v>300</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+1080</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>[R23] Hound †</t>
+          <t>Razor Sunkaze</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>300</v>
+        <v>6126</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+843</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Razor Sunkaze</t>
+          <t>Haise</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>6126</v>
+        <v>27271</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+843</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Haise</t>
+          <t>Andres R</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>27271</v>
+        <v>0</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Andres R</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -49,6 +49,7 @@
     <sheet name="2026-08-24" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-25" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-26" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="2026-08-27" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32742,6 +32743,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-27 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12069</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>20990</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>34619</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2221</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>551</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2889</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>28211</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>11425</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5882</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4948</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>27741</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1841</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TipeneMartipene</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>6958</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>35373</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2817</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>57886</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>55362</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>58286</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>63960</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2573</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>17850</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2520</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2466</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>43306</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44586</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2521</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>15719</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+537</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>46728</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>7510</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1384</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -32767,7 +32767,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-27 13:01:00</t>
+          <t>Timestamp: 2026-08-27 13:31:00</t>
         </is>
       </c>
     </row>
@@ -33065,11 +33065,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+300</t>
+          <t>+420</t>
         </is>
       </c>
     </row>
@@ -33095,11 +33095,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+360</t>
+          <t>+420</t>
         </is>
       </c>
     </row>
@@ -33155,11 +33155,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+300</t>
+          <t>+360</t>
         </is>
       </c>
     </row>
@@ -33305,11 +33305,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>35373</v>
+        <v>35433</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+2817</t>
+          <t>+2877</t>
         </is>
       </c>
     </row>
@@ -33335,11 +33335,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>55362</v>
+        <v>55382</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+2880</t>
+          <t>+2900</t>
         </is>
       </c>
     </row>
@@ -33350,11 +33350,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>58286</v>
+        <v>58346</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+2880</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -33380,11 +33380,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>63960</v>
+        <v>64020</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2573</t>
+          <t>+2633</t>
         </is>
       </c>
     </row>
@@ -33500,11 +33500,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>43306</v>
+        <v>43486</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+840</t>
+          <t>+1020</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -50,6 +50,7 @@
     <sheet name="2026-08-25" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-26" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-27" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="2026-08-28" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33622,6 +33623,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-28 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12069</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+780</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>21290</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>36863</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2244</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1231</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4029</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>29291</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>13010</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1585</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5882</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>5248</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1620</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>29721</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TipeneMartipene</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>7318</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>37821</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2388</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>60646</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2760</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57942</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2560</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>61046</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+2700</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>66180</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2160</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>20670</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>21906</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2826</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>45103</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1617</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>46866</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2280</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>16079</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>48921</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2193</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+740</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -51,6 +51,7 @@
     <sheet name="2026-08-26" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-27" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-28" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="2026-08-29" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34502,6 +34503,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-29 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12069</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>22440</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>38905</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2042</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2264</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+482</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>818</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+798</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4449</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30491</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>14328</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1318</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>953</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kiroi Senko</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5882</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5248</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2484</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+864</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>30663</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+942</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>7918</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>40605</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2784</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>63596</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2950</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>60892</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2950</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>63936</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2890</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>69092</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2912</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1542</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23541</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2871</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24786</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>45454</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+351</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>49317</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2451</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>16739</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>50642</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1721</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>9360</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>27271</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Andres R</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -34527,7 +34527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-29 13:01:00</t>
+          <t>Timestamp: 2026-08-29 13:31:00</t>
         </is>
       </c>
     </row>
@@ -34720,11 +34720,11 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>818</v>
+        <v>3569</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+798</t>
+          <t>+3549</t>
         </is>
       </c>
     </row>
@@ -34840,11 +34840,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>14328</v>
+        <v>14928</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+1318</t>
+          <t>+1918</t>
         </is>
       </c>
     </row>
@@ -34900,11 +34900,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>5882</v>
+        <v>6482</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+600</t>
         </is>
       </c>
     </row>
@@ -35050,11 +35050,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>40605</v>
+        <v>40725</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+2784</t>
+          <t>+2904</t>
         </is>
       </c>
     </row>
@@ -35065,11 +35065,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>63596</v>
+        <v>63636</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+2950</t>
+          <t>+2990</t>
         </is>
       </c>
     </row>
@@ -35125,11 +35125,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>69092</v>
+        <v>69212</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+2912</t>
+          <t>+3032</t>
         </is>
       </c>
     </row>
@@ -35185,11 +35185,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>23541</v>
+        <v>23901</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2871</t>
+          <t>+3231</t>
         </is>
       </c>
     </row>
@@ -35335,11 +35335,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>9360</v>
+        <v>9840</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+1110</t>
+          <t>+1590</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -52,6 +52,7 @@
     <sheet name="2026-08-27" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-28" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-08-29" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="2026-08-30" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35382,6 +35383,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-30 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+18407</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>13492</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+13492</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>26769</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+14700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>21254</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+19994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>21423</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+20410</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34186</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+11746</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54262</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+15357</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10789</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+10789</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>25264</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+23000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>17179</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+17138</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>17537</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>21740</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+21140</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>17951</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+14382</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>27612</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+23163</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>12930</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+12930</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>26424</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+26424</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>13013</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+12901</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>13394</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+13394</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>52543</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+22052</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>24582</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+23202</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>40434</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+25506</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>23861</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+22541</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>19405</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+18452</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>18695</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+18635</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>18097</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+12849</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>25734</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+23250</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>22719</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>60044</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+29381</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21889</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+21889</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>21468</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+21362</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20824</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+20824</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>13729</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+13709</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>11154</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+11114</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>33465</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+25547</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>60537</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+19812</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>89056</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+25420</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>86476</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+25584</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>85672</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+21736</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>21523</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+21523</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>98237</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+29025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19880</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+19630</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>30039</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+28497</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>24403</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+24403</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>44310</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+20409</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>24372</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+24372</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>33903</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+33903</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>34548</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+34548</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+18814</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>55973</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+10519</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>73565</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+24248</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>57543</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+40804</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>61003</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+10361</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>22118</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+20978</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>25027</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+15187</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>39956</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+12685</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -35407,7 +35407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-30 13:01:00</t>
+          <t>Timestamp: 2026-08-30 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -53,6 +53,7 @@
     <sheet name="2026-08-28" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-08-29" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-08-30" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="2026-08-31" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36262,6 +36263,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-31 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>13492</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>26769</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>21254</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>21423</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34186</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54262</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10789</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>25264</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>17179</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>17537</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>21740</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>17951</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>27612</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>12930</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>26424</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>13013</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>13394</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>52543</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>24582</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A K A G A M I</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>40434</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>23861</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>19405</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>18695</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>18097</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>25734</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>22719</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>60044</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21889</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>21468</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20824</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>13729</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>11154</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>33465</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>60537</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>89056</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>86476</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>85672</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>21523</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>98237</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19880</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>30039</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>24403</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>44310</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>24372</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>33903</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>34548</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>55973</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>73565</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>57543</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>61003</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>22118</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>25027</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>39956</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -36287,7 +36287,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-31 13:01:00</t>
+          <t>Timestamp: 2026-08-31 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -54,6 +54,7 @@
     <sheet name="2026-08-29" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-08-30" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-08-31" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="2026-09-01" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37142,6 +37143,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-01 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>13492</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>26769</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>21254</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>21423</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34186</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54262</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10789</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>25264</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>17179</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>17537</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>21740</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>17951</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>27612</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>12930</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>26424</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>13013</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>13394</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>52543</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>24582</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobta </t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>40434</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>23861</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>19405</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>18695</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>18097</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>25734</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>22719</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>60044</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21889</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>21468</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20824</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>13729</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>11154</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>33465</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>60537</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>89056</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>86476</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>85672</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>21523</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>98237</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19880</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>30039</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>24403</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>44310</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>24372</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>33903</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>34548</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>43600</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>55973</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>73565</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>57543</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>61003</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>22118</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>25027</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>39956</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -37167,7 +37167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-01 13:01:00</t>
+          <t>Timestamp: 2026-09-01 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -55,6 +55,7 @@
     <sheet name="2026-08-30" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-08-31" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-09-01" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="2026-09-02" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38022,6 +38023,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-02 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>-19007</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>-13492</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>-26769</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>-21254</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>-21423</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-33823</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Kyara Senju™</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>-54012</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-10789</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>-25264</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-17179</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>-17537</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>-21740</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>-17951</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>-27612</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>-12930</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>-26424</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>-13013</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>-13394</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>-52543</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>-24582</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobta </t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>-40434</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>-23826</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>-19405</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>-18695</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>-18097</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>-25734</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-22719</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-60044</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>-21889</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>-21468</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>-20824</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-13729</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>-11154</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>-33093</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>-60177</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>-89056</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>-86476</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>-85672</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>-21523</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>-98237</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>-19880</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>-30039</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>-24403</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-44310</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>-24372</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>-33903</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>-34478</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>-43600</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>-55973</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>-73565</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>-57231</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>-61003</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>-22118</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>-24806</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>-39956</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -38047,7 +38047,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-02 13:01:00</t>
+          <t>Timestamp: 2026-09-02 13:31:01</t>
         </is>
       </c>
     </row>
@@ -38210,11 +38210,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>-17179</t>
+          <t>-17165</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -56,6 +56,7 @@
     <sheet name="2026-08-31" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-09-01" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-02" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="2026-09-03" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39781,6 +39782,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-03 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>723</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+255</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobta </t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2152</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+2152</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+368</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2234</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1874</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>2852</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+2852</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2958</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2958</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+280</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+476</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>984</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+984</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BlacKEucresia Ó</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1397</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>803</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+582</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -39806,7 +39806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-03 13:01:00</t>
+          <t>Timestamp: 2026-09-03 13:31:00</t>
         </is>
       </c>
     </row>
@@ -40374,11 +40374,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>2958</v>
+        <v>3028</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+2958</t>
+          <t>+3028</t>
         </is>
       </c>
     </row>
@@ -40419,11 +40419,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>476</v>
+        <v>546</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+476</t>
+          <t>+546</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -57,6 +57,7 @@
     <sheet name="2026-09-01" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-02" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-09-03" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="2026-09-04" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40661,6 +40662,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-04 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>725</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1468</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobta </t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3676</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1524</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2947</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+952</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1040</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>4698</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2464</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+932</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+870</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3387</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2841</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>984</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>WA CHI CHAO</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2466</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3921</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2381</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3112</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2762</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2762</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1779</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+976</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -40686,7 +40686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-04 13:01:00</t>
+          <t>Timestamp: 2026-09-04 13:31:00</t>
         </is>
       </c>
     </row>
@@ -40789,11 +40789,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>725</v>
+        <v>1025</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+302</t>
         </is>
       </c>
     </row>
@@ -40969,11 +40969,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1723</v>
+        <v>1823</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1468</t>
+          <t>+1568</t>
         </is>
       </c>
     </row>
@@ -41299,11 +41299,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>3387</v>
+        <v>3437</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2841</t>
+          <t>+2891</t>
         </is>
       </c>
     </row>
@@ -41449,11 +41449,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>3921</v>
+        <v>3971</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+2381</t>
+          <t>+2431</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -58,6 +58,7 @@
     <sheet name="2026-09-02" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-09-03" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-09-04" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="2026-09-05" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41541,6 +41542,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-05 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1839</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+814</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+232</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3468</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+1645</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobta </t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4999</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1323</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4479</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1532</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku ™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2141</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>6058</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1360</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A n T z</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>5715</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2278</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2937</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>4276</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1810</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>5613</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1642</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>4167</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>4517</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1755</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+1469</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -41566,7 +41566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-05 13:01:00</t>
+          <t>Timestamp: 2026-09-05 13:31:00</t>
         </is>
       </c>
     </row>
@@ -41834,11 +41834,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>3468</v>
+        <v>3568</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+1645</t>
+          <t>+1745</t>
         </is>
       </c>
     </row>
@@ -42059,11 +42059,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>2141</v>
+        <v>2341</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+1101</t>
+          <t>+1301</t>
         </is>
       </c>
     </row>
@@ -42074,11 +42074,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>6058</v>
+        <v>6158</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+1360</t>
+          <t>+1460</t>
         </is>
       </c>
     </row>
@@ -42179,11 +42179,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>5715</v>
+        <v>5815</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2278</t>
+          <t>+2378</t>
         </is>
       </c>
     </row>
@@ -42314,11 +42314,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>4276</v>
+        <v>4376</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1810</t>
+          <t>+1910</t>
         </is>
       </c>
     </row>
@@ -42329,11 +42329,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>5613</v>
+        <v>5713</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1642</t>
+          <t>+1742</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -59,6 +59,7 @@
     <sheet name="2026-09-03" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-09-04" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="2026-09-05" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="2026-09-06" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42421,6 +42422,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-06 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4819</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+2980</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>732</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8478</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+4910</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>6779</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>8638</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+4159</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3939</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1598</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>11142</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+4984</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A n T z</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>11024</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+5209</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5269</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2332</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>7188</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2812</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8566</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2853</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5607</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>9822</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5305</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+981</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -42446,7 +42446,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-06 13:01:00</t>
+          <t>Timestamp: 2026-09-06 13:31:00</t>
         </is>
       </c>
     </row>
@@ -42534,11 +42534,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4819</v>
+        <v>5443</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+2980</t>
+          <t>+3604</t>
         </is>
       </c>
     </row>
@@ -42714,11 +42714,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>8478</v>
+        <v>8678</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+4910</t>
+          <t>+5110</t>
         </is>
       </c>
     </row>
@@ -42939,11 +42939,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>3939</v>
+        <v>4340</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+1598</t>
+          <t>+1999</t>
         </is>
       </c>
     </row>
@@ -42954,11 +42954,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>11142</v>
+        <v>11458</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+4984</t>
+          <t>+5300</t>
         </is>
       </c>
     </row>
@@ -43059,11 +43059,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>11024</v>
+        <v>11224</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+5209</t>
+          <t>+5409</t>
         </is>
       </c>
     </row>
@@ -43209,11 +43209,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>8566</v>
+        <v>9066</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+2853</t>
+          <t>+3353</t>
         </is>
       </c>
     </row>
@@ -43269,11 +43269,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3010</v>
+        <v>3092</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+981</t>
+          <t>+1063</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -60,6 +60,7 @@
     <sheet name="2026-09-04" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="2026-09-05" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="2026-09-06" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="2026-09-07" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43301,6 +43302,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-07 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>843</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+843</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>7407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1964</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>843</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+843</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11638</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2960</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>8279</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>916</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+881</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>881</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+881</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SharinganKniGhT™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>10635</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1997</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>13598</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2140</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>SB | A n T z</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>16756</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+5532</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>RS | Jmplng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>943</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+943</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5269</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>12770</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+5582</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>13686</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+4620</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6307</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+700</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>14379</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4557</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>4393</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1301</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -43326,7 +43326,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-07 13:01:00</t>
+          <t>Timestamp: 2026-09-07 13:31:00</t>
         </is>
       </c>
     </row>
@@ -43639,11 +43639,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>8279</v>
+        <v>8552</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+1500</t>
+          <t>+1773</t>
         </is>
       </c>
     </row>
@@ -43954,11 +43954,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>16756</v>
+        <v>16788</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+5532</t>
+          <t>+5564</t>
         </is>
       </c>
     </row>
@@ -43969,11 +43969,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>943</v>
+        <v>1043</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+943</t>
+          <t>+1043</t>
         </is>
       </c>
     </row>
@@ -44074,11 +44074,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>12770</v>
+        <v>12811</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+5582</t>
+          <t>+5623</t>
         </is>
       </c>
     </row>
@@ -44119,11 +44119,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>14379</v>
+        <v>14429</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+4557</t>
+          <t>+4607</t>
         </is>
       </c>
     </row>
@@ -44149,11 +44149,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>4393</v>
+        <v>4593</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+1301</t>
+          <t>+1501</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -61,6 +61,7 @@
     <sheet name="2026-09-05" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="2026-09-06" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="2026-09-07" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="2026-09-08" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44181,6 +44182,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-08 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1763</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+183</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2303</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1460</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>7689</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+282</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1867</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>12788</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>9352</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+800</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>916</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1981</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>10955</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+320</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>15080</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SB | A n T z</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>18747</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>5269</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>14953</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2142</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>15255</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1569</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>6907</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>16553</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2124</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Razor Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5098</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+505</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -44206,7 +44206,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-08 13:01:00</t>
+          <t>Timestamp: 2026-09-08 13:31:00</t>
         </is>
       </c>
     </row>
@@ -44489,11 +44489,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>12788</v>
+        <v>12838</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1150</t>
+          <t>+1200</t>
         </is>
       </c>
     </row>
@@ -44519,11 +44519,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>9352</v>
+        <v>9652</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+1100</t>
         </is>
       </c>
     </row>
@@ -44819,11 +44819,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>18747</v>
+        <v>18797</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+1959</t>
+          <t>+2009</t>
         </is>
       </c>
     </row>
@@ -44984,11 +44984,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>16553</v>
+        <v>16603</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+2124</t>
+          <t>+2174</t>
         </is>
       </c>
     </row>
@@ -45014,11 +45014,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>5098</v>
+        <v>5180</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+505</t>
+          <t>+587</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -62,6 +62,7 @@
     <sheet name="2026-09-06" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="2026-09-07" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="2026-09-08" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="2026-09-09" sheetId="56" state="visible" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45046,6 +45047,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-09 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2736</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+973</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3490</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1187</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8289</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2736</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+869</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>14038</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3550</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>10502</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+850</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1366</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+450</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3345</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>12655</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1700</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5290</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+350</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>16330</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SB | A n T z</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>21147</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+1896</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>4063</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1492</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>6743</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1474</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>17222</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2269</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>17606</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2351</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>7557</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+650</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>18650</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2047</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>6192</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -45071,7 +45071,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-09 13:01:00</t>
+          <t>Timestamp: 2026-09-09 13:31:00</t>
         </is>
       </c>
     </row>
@@ -45129,11 +45129,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2736</v>
+        <v>2816</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+973</t>
+          <t>+1053</t>
         </is>
       </c>
     </row>
@@ -45684,11 +45684,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>21147</v>
+        <v>21197</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2350</t>
+          <t>+2400</t>
         </is>
       </c>
     </row>
@@ -45729,11 +45729,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>4063</v>
+        <v>4163</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+1492</t>
+          <t>+1592</t>
         </is>
       </c>
     </row>
@@ -45804,11 +45804,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>17222</v>
+        <v>17272</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2269</t>
+          <t>+2319</t>
         </is>
       </c>
     </row>
@@ -45819,11 +45819,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>17606</v>
+        <v>17656</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2351</t>
+          <t>+2401</t>
         </is>
       </c>
     </row>
@@ -45849,11 +45849,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>18650</v>
+        <v>18700</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+2047</t>
+          <t>+2097</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -63,6 +63,7 @@
     <sheet name="2026-09-07" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="2026-09-08" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="2026-09-09" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="2026-09-10" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45911,6 +45912,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-10 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4027</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+1211</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1142</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8589</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1682</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+541</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>15743</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1705</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>10802</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+787</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>14005</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1350</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5851</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+561</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>18376</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>23484</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2287</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>7513</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2573</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>6350</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2187</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9044</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2301</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>18386</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>19229</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1573</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8157</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>19620</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+920</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>6442</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -45936,7 +45936,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-10 13:01:00</t>
+          <t>Timestamp: 2026-09-10 13:31:00</t>
         </is>
       </c>
     </row>
@@ -46219,11 +46219,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>15743</v>
+        <v>15793</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1705</t>
+          <t>+1755</t>
         </is>
       </c>
     </row>
@@ -46429,11 +46429,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>5851</v>
+        <v>6071</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+561</t>
+          <t>+781</t>
         </is>
       </c>
     </row>
@@ -46549,11 +46549,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>23484</v>
+        <v>23534</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2287</t>
+          <t>+2337</t>
         </is>
       </c>
     </row>
@@ -46654,11 +46654,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>9044</v>
+        <v>9094</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+2301</t>
+          <t>+2351</t>
         </is>
       </c>
     </row>
@@ -46669,11 +46669,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>18386</v>
+        <v>18536</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1114</t>
+          <t>+1264</t>
         </is>
       </c>
     </row>
@@ -46684,11 +46684,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>19229</v>
+        <v>19289</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1573</t>
+          <t>+1633</t>
         </is>
       </c>
     </row>
@@ -46714,11 +46714,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>19620</v>
+        <v>19820</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+920</t>
+          <t>+1120</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -64,6 +64,7 @@
     <sheet name="2026-09-08" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="2026-09-09" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="2026-09-10" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="2026-09-11" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46776,6 +46777,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-11 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8889</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>17348</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1555</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>11442</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+640</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>15325</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>6872</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+801</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>19818</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1442</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>25884</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>8013</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>8555</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2205</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>11172</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2078</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>20382</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1846</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20831</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1542</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8457</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>21720</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>7592</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2119</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+650</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -46801,7 +46801,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-11 13:01:00</t>
+          <t>Timestamp: 2026-09-11 13:31:00</t>
         </is>
       </c>
     </row>
@@ -47414,11 +47414,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>25884</v>
+        <v>25934</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2350</t>
+          <t>+2400</t>
         </is>
       </c>
     </row>
@@ -47429,11 +47429,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>8013</v>
+        <v>8313</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>+800</t>
         </is>
       </c>
     </row>
@@ -47459,11 +47459,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>8555</v>
+        <v>8655</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2205</t>
+          <t>+2305</t>
         </is>
       </c>
     </row>
@@ -47519,11 +47519,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>11172</v>
+        <v>11322</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+2078</t>
+          <t>+2228</t>
         </is>
       </c>
     </row>
@@ -47534,11 +47534,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>20382</v>
+        <v>20432</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1846</t>
+          <t>+1896</t>
         </is>
       </c>
     </row>
@@ -47549,11 +47549,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>20831</v>
+        <v>20881</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1542</t>
+          <t>+1592</t>
         </is>
       </c>
     </row>
@@ -47624,11 +47624,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>2119</v>
+        <v>2169</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+650</t>
+          <t>+700</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -65,6 +65,7 @@
     <sheet name="2026-09-09" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="2026-09-10" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="2026-09-11" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="2026-09-12" sheetId="59" state="visible" r:id="rId59"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47641,6 +47642,870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-12 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>9381</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+492</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>18444</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>11842</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+400</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>16613</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1288</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>7172</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>20964</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1146</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>620</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>28122</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+2188</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>10474</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2161</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>10242</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>12768</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1446</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>21133</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+701</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>23105</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2224</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>9057</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>22270</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+550</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>8133</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+541</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3260</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1091</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -47666,7 +47666,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-12 13:01:00</t>
+          <t>Timestamp: 2026-09-12 13:31:00</t>
         </is>
       </c>
     </row>
@@ -48279,11 +48279,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>28122</v>
+        <v>28222</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+2188</t>
+          <t>+2288</t>
         </is>
       </c>
     </row>
@@ -48294,11 +48294,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>10474</v>
+        <v>10614</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2161</t>
+          <t>+2301</t>
         </is>
       </c>
     </row>
@@ -48384,11 +48384,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>12768</v>
+        <v>13068</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1446</t>
+          <t>+1746</t>
         </is>
       </c>
     </row>
@@ -48414,11 +48414,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>23105</v>
+        <v>23205</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2224</t>
+          <t>+2324</t>
         </is>
       </c>
     </row>
@@ -48489,11 +48489,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3260</v>
+        <v>3360</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+1091</t>
+          <t>+1191</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -66,6 +66,7 @@
     <sheet name="2026-09-10" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="2026-09-11" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="2026-09-12" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="2026-09-13" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49385,6 +49386,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-13 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>12381</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>22706</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+4262</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>12642</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+800</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>19694</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+3081</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>7854</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+682</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>22864</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>620</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>32846</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+4624</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2248</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>14509</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+4267</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>16893</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3825</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24714</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3581</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>25482</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2277</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>9486</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+429</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>25847</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3577</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>9857</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1724</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -49410,7 +49410,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-13 13:01:00</t>
+          <t>Timestamp: 2026-09-13 13:31:00</t>
         </is>
       </c>
     </row>
@@ -49693,11 +49693,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>22706</v>
+        <v>22773</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+4262</t>
+          <t>+4329</t>
         </is>
       </c>
     </row>
@@ -50038,11 +50038,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>32846</v>
+        <v>32946</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+4624</t>
+          <t>+4724</t>
         </is>
       </c>
     </row>
@@ -50083,11 +50083,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>14509</v>
+        <v>14629</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+4267</t>
+          <t>+4387</t>
         </is>
       </c>
     </row>
@@ -50143,11 +50143,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>16893</v>
+        <v>17193</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3825</t>
+          <t>+4125</t>
         </is>
       </c>
     </row>
@@ -50158,11 +50158,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>24714</v>
+        <v>25114</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3581</t>
+          <t>+3981</t>
         </is>
       </c>
     </row>
@@ -50203,11 +50203,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>25847</v>
+        <v>25867</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+3577</t>
+          <t>+3597</t>
         </is>
       </c>
     </row>
